--- a/artfynd/A 42610-2023 artfynd.xlsx
+++ b/artfynd/A 42610-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42610-2023 artfynd.xlsx
+++ b/artfynd/A 42610-2023 artfynd.xlsx
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112551570</v>
+        <v>112551611</v>
       </c>
       <c r="B2" t="n">
-        <v>55732</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öster Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>378345</v>
+        <v>378093</v>
       </c>
       <c r="R2" t="n">
-        <v>6699620</v>
+        <v>6699455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,50 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112551611</v>
+        <v>112551570</v>
       </c>
       <c r="B3" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öster Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>378093</v>
+        <v>378345</v>
       </c>
       <c r="R3" t="n">
-        <v>6699454</v>
+        <v>6699619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 42610-2023 artfynd.xlsx
+++ b/artfynd/A 42610-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551611</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,8 +885,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551570</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>